--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67A4909-EE2A-4A2F-8BA5-151DF4B9129A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB51A893-D6F8-4D9B-8B9F-73F61E2F49D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="191">
   <si>
     <t>DE SETOR</t>
   </si>
@@ -3548,6 +3548,12 @@
   </si>
   <si>
     <t>0331 - HS MALETA DE TRANSP UTI GERAL2</t>
+  </si>
+  <si>
+    <t>0035 - ENGENHARIA PREDIAL</t>
+  </si>
+  <si>
+    <t>ENGENHARIA PREDIAL</t>
   </si>
 </sst>
 </file>
@@ -6109,6 +6115,17 @@
         <v>HS MALETA DE TRANSP UTI GERAL2</v>
       </c>
     </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
     <row r="181" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A181"/>
     </row>

--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB51A893-D6F8-4D9B-8B9F-73F61E2F49D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A1F0CD-2C17-42C6-9B63-C28C91547320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="195">
   <si>
     <t>DE SETOR</t>
   </si>
@@ -3554,6 +3554,18 @@
   </si>
   <si>
     <t>ENGENHARIA PREDIAL</t>
+  </si>
+  <si>
+    <t>0335 - TC INTERVENCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TC INTERVENCAO</t>
+  </si>
+  <si>
+    <t>0089 - HV CARRO PARADA PED ALA2</t>
+  </si>
+  <si>
+    <t>HV CARRO PARADA PED ALA2</t>
   </si>
 </sst>
 </file>
@@ -3584,7 +3596,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3603,8 +3615,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3612,16 +3630,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6127,10 +6157,26 @@
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A181"/>
+      <c r="A181" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="182" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A182"/>
+      <c r="A182" t="s">
+        <v>193</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A183"/>

--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A1F0CD-2C17-42C6-9B63-C28C91547320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A0DDDA-2F09-448A-891A-6BF5E54341BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -6161,7 +6161,7 @@
         <v>191</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>192</v>

--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A0DDDA-2F09-448A-891A-6BF5E54341BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BE84B0-68C4-4A3F-B043-648F42DC33BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="196">
   <si>
     <t>DE SETOR</t>
   </si>
@@ -3566,6 +3566,9 @@
   </si>
   <si>
     <t>HV CARRO PARADA PED ALA2</t>
+  </si>
+  <si>
+    <t>0204 - HV LABORATORIO</t>
   </si>
 </sst>
 </file>
@@ -6179,7 +6182,16 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A183"/>
+      <c r="A183" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" s="2" t="str">
+        <f t="shared" ref="C183" si="3">MID(A183,8,1000)</f>
+        <v>HV LABORATORIO</v>
+      </c>
     </row>
     <row r="184" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A184"/>

--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BE84B0-68C4-4A3F-B043-648F42DC33BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21E4D2BC-103E-4037-A64C-4B5EA73299E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="191">
   <si>
     <t>DE SETOR</t>
   </si>
@@ -3550,25 +3550,10 @@
     <t>0331 - HS MALETA DE TRANSP UTI GERAL2</t>
   </si>
   <si>
-    <t>0035 - ENGENHARIA PREDIAL</t>
-  </si>
-  <si>
-    <t>ENGENHARIA PREDIAL</t>
-  </si>
-  <si>
-    <t>0335 - TC INTERVENCAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TC INTERVENCAO</t>
-  </si>
-  <si>
-    <t>0089 - HV CARRO PARADA PED ALA2</t>
-  </si>
-  <si>
-    <t>HV CARRO PARADA PED ALA2</t>
-  </si>
-  <si>
-    <t>0204 - HV LABORATORIO</t>
+    <t>0334 - SEMI UI - BL B - 2 ANDAR</t>
+  </si>
+  <si>
+    <t>SEMI</t>
   </si>
 </sst>
 </file>
@@ -3599,7 +3584,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3616,12 +3601,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -3654,7 +3633,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5556,7 +5535,7 @@
         <v>13</v>
       </c>
       <c r="C130" t="str">
-        <f t="shared" ref="C130:C179" si="2">MID(A130,8,1000)</f>
+        <f t="shared" ref="C130:C180" si="2">MID(A130,8,1000)</f>
         <v>UI TMO ADULTO - BL C - 1 ANDAR</v>
       </c>
     </row>
@@ -6148,50 +6127,26 @@
         <v>HS MALETA DE TRANSP UTI GERAL2</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2" t="s">
+    <row r="180" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
         <v>189</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C180" s="2" t="s">
         <v>190</v>
       </c>
+      <c r="C180" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SEMI UI - BL B - 2 ANDAR</v>
+      </c>
     </row>
     <row r="181" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A181" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>192</v>
-      </c>
+      <c r="A181"/>
     </row>
     <row r="182" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>193</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>194</v>
-      </c>
+      <c r="A182"/>
     </row>
     <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A183" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C183" s="2" t="str">
-        <f t="shared" ref="C183" si="3">MID(A183,8,1000)</f>
-        <v>HV LABORATORIO</v>
-      </c>
+      <c r="A183"/>
     </row>
     <row r="184" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A184"/>

--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21E4D2BC-103E-4037-A64C-4B5EA73299E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B15F69F9-6761-4538-855D-49BB29D91997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="193">
   <si>
     <t>DE SETOR</t>
   </si>
@@ -3554,6 +3554,12 @@
   </si>
   <si>
     <t>SEMI</t>
+  </si>
+  <si>
+    <t>0204 - HV LABORATORIO</t>
+  </si>
+  <si>
+    <t>0335 - TC INTERVENCAO</t>
   </si>
 </sst>
 </file>
@@ -3584,7 +3590,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3597,14 +3603,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3612,28 +3612,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5535,7 +5521,7 @@
         <v>13</v>
       </c>
       <c r="C130" t="str">
-        <f t="shared" ref="C130:C180" si="2">MID(A130,8,1000)</f>
+        <f t="shared" ref="C130:C182" si="2">MID(A130,8,1000)</f>
         <v>UI TMO ADULTO - BL C - 1 ANDAR</v>
       </c>
     </row>
@@ -5864,286 +5850,304 @@
       </c>
     </row>
     <row r="158" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A158" s="3" t="s">
+      <c r="A158" t="s">
         <v>166</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C158" s="3" t="str">
+      <c r="C158" t="str">
         <f t="shared" si="2"/>
         <v>CTI ADULTO</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A159" s="3" t="s">
+      <c r="A159" t="s">
         <v>167</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C159" s="3" t="str">
+      <c r="C159" t="str">
         <f t="shared" si="2"/>
         <v>4 ANDAR</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A160" s="3" t="s">
+      <c r="A160" t="s">
         <v>168</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C160" s="3" t="str">
+      <c r="C160" t="str">
         <f t="shared" si="2"/>
         <v>CENTRO CIRURGICO</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A161" s="3" t="s">
+      <c r="A161" t="s">
         <v>169</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C161" s="3" t="str">
+      <c r="C161" t="str">
         <f t="shared" si="2"/>
         <v>MATERNIDADE 2 ANDAR</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A162" s="3" t="s">
+      <c r="A162" t="s">
         <v>170</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C162" s="3" t="str">
+      <c r="C162" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> U.T.I. NEONATAL</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A163" s="3" t="s">
+      <c r="A163" t="s">
         <v>171</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C163" s="3" t="str">
+      <c r="C163" t="str">
         <f t="shared" si="2"/>
         <v>LABORATORIO</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A164" s="3" t="s">
+      <c r="A164" t="s">
         <v>172</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="3" t="str">
+      <c r="C164" t="str">
         <f t="shared" si="2"/>
         <v>RADIOLOGIA</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A165" s="3" t="s">
+      <c r="A165" t="s">
         <v>173</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C165" s="3" t="str">
+      <c r="C165" t="str">
         <f t="shared" si="2"/>
         <v>3 ANDAR</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A166" s="3" t="s">
+      <c r="A166" t="s">
         <v>174</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C166" s="3" t="str">
+      <c r="C166" t="str">
         <f t="shared" si="2"/>
         <v>TERREO</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A167" s="3" t="s">
+      <c r="A167" t="s">
         <v>175</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C167" s="3" t="str">
+      <c r="C167" t="str">
         <f t="shared" si="2"/>
         <v>UH STL-RECEP SADT/UNDIG - RC</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A168" s="3" t="s">
+      <c r="A168" t="s">
         <v>176</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C168" s="3" t="str">
+      <c r="C168" t="str">
         <f t="shared" si="2"/>
         <v>1 ANDAR</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A169" s="3" t="s">
+      <c r="A169" t="s">
         <v>177</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C169" s="3" t="str">
+      <c r="C169" t="str">
         <f t="shared" si="2"/>
         <v>PSGO</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A170" s="3" t="s">
+      <c r="A170" t="s">
         <v>178</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C170" s="3" t="str">
+      <c r="C170" t="str">
         <f t="shared" si="2"/>
         <v>AMBULATORIO</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
+      <c r="A171" t="s">
         <v>179</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C171" s="3" t="str">
+      <c r="C171" t="str">
         <f t="shared" si="2"/>
         <v>DAY CLINIC</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A172" s="3" t="s">
+      <c r="A172" t="s">
         <v>180</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C172" s="3" t="str">
+      <c r="C172" t="str">
         <f t="shared" si="2"/>
         <v>BERCARIO</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A173" s="3" t="s">
+      <c r="A173" t="s">
         <v>181</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C173" s="3" t="str">
+      <c r="C173" t="str">
         <f t="shared" si="2"/>
         <v>PSA</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A174" s="3" t="s">
+      <c r="A174" t="s">
         <v>182</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C174" s="3" t="str">
+      <c r="C174" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> SAUDE SANTA LUCIA S/A</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A175" s="3" t="s">
+      <c r="A175" t="s">
         <v>183</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C175" s="3" t="str">
+      <c r="C175" t="str">
         <f t="shared" si="2"/>
         <v>CENTRO OBSTÉTRICO</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A176" s="3" t="s">
+      <c r="A176" t="s">
         <v>184</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C176" s="3" t="str">
+      <c r="C176" t="str">
         <f t="shared" si="2"/>
         <v>KIT CATASTROFE</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A177" s="3" t="s">
+      <c r="A177" t="s">
         <v>186</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C177" s="3" t="str">
+      <c r="C177" t="str">
         <f t="shared" si="2"/>
         <v>DIÁLISE PERI AMBU - SMB</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A178" s="3" t="s">
+      <c r="A178" t="s">
         <v>187</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C178" s="3" t="str">
+      <c r="C178" t="str">
         <f t="shared" si="2"/>
         <v>ESTOQUE OPME</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A179" s="3" t="s">
+      <c r="A179" t="s">
         <v>188</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C179" s="3" t="str">
+      <c r="C179" t="str">
         <f t="shared" si="2"/>
         <v>HS MALETA DE TRANSP UTI GERAL2</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A180" s="5" t="s">
+      <c r="A180" t="s">
         <v>189</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C180" s="3" t="str">
+      <c r="C180" t="str">
         <f t="shared" si="2"/>
         <v>SEMI UI - BL B - 2 ANDAR</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A181"/>
+      <c r="A181" t="s">
+        <v>191</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181" t="str">
+        <f t="shared" si="2"/>
+        <v>HV LABORATORIO</v>
+      </c>
     </row>
     <row r="182" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A182"/>
+      <c r="A182" t="s">
+        <v>192</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="str">
+        <f t="shared" si="2"/>
+        <v>TC INTERVENCAO</v>
+      </c>
     </row>
     <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A183"/>

--- a/DE PARA SETOR.xlsx
+++ b/DE PARA SETOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alclima\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B15F69F9-6761-4538-855D-49BB29D91997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F078B93-AFE0-4E7E-BB41-0B6ED4510A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31F185F4-8632-4281-BBEC-0EAFCF2BD7F6}"/>
   </bookViews>
@@ -2981,7 +2981,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="194">
   <si>
     <t>DE SETOR</t>
   </si>
@@ -3560,6 +3560,9 @@
   </si>
   <si>
     <t>0335 - TC INTERVENCAO</t>
+  </si>
+  <si>
+    <t>0033 - CME ESTERILIZACAO</t>
   </si>
 </sst>
 </file>
@@ -5521,7 +5524,7 @@
         <v>13</v>
       </c>
       <c r="C130" t="str">
-        <f t="shared" ref="C130:C182" si="2">MID(A130,8,1000)</f>
+        <f t="shared" ref="C130:C183" si="2">MID(A130,8,1000)</f>
         <v>UI TMO ADULTO - BL C - 1 ANDAR</v>
       </c>
     </row>
@@ -6150,7 +6153,16 @@
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A183"/>
+      <c r="A183" t="s">
+        <v>193</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" t="str">
+        <f t="shared" si="2"/>
+        <v>CME ESTERILIZACAO</v>
+      </c>
     </row>
     <row r="184" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A184"/>
